--- a/db/templates/inbound_delivery_default.xlsx
+++ b/db/templates/inbound_delivery_default.xlsx
@@ -10,6 +10,9 @@
     <sheet name="Goods Receipt" sheetId="1" r:id="rId1"/>
     <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Goods Receipt'!$1:$13</definedName>
+  </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
@@ -763,6 +766,10 @@
     <mergeCell ref="A14:B14"/>
   </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
+    <evenFooter>&amp;CPage &amp;P of &amp;N</evenFooter>
+  </headerFooter>
 </worksheet>
 </file>
 

--- a/db/templates/inbound_delivery_default.xlsx
+++ b/db/templates/inbound_delivery_default.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>{{vendor.name}}</t>
   </si>
@@ -279,6 +279,27 @@
   </si>
   <si>
     <t>Free-text notes, blank if unset</t>
+  </si>
+  <si>
+    <t>Export info</t>
+  </si>
+  <si>
+    <t>{{export.generatedDate}}</t>
+  </si>
+  <si>
+    <t>Date this file was exported (not the receipt's own date), in the organization's date format</t>
+  </si>
+  <si>
+    <t>{{export.generatedTime}}</t>
+  </si>
+  <si>
+    <t>Time this file was exported, 24-hour HH:MM, server time</t>
+  </si>
+  <si>
+    <t>&amp;P (page number) / &amp;N (total pages)</t>
+  </si>
+  <si>
+    <t>Native Excel/LibreOffice codes, not a {{}} placeholder — only work inside this sheet's own Page Layout ▸ Header/Footer, never in a regular cell, since the page count isn't known until export. The default footer already shows "Page &amp;P of &amp;N" on every page; edit it in Excel/LibreOffice's own header/footer editor to move or restyle it</t>
   </si>
 </sst>
 </file>
@@ -1058,12 +1079,42 @@
         <v>86</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A38:C38"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/db/templates/inbound_delivery_default.xlsx
+++ b/db/templates/inbound_delivery_default.xlsx
@@ -763,13 +763,13 @@
       <c r="A14" t="s">
         <v>20</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F14" t="s">

--- a/db/templates/inbound_delivery_default.xlsx
+++ b/db/templates/inbound_delivery_default.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>{{vendor.name}}</t>
   </si>
@@ -68,6 +68,9 @@
     <t>VAT: {{organization.vatin}}</t>
   </si>
   <si>
+    <t>Product</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
@@ -80,6 +83,9 @@
     <t>Line Total</t>
   </si>
   <si>
+    <t>{{lineItems.sku}}</t>
+  </si>
+  <si>
     <t>{{lineItems.description}}</t>
   </si>
   <si>
@@ -249,6 +255,9 @@
   </si>
   <si>
     <t>Marker (not a value) — place alone in any one cell of the row to repeat once per line item; that whole cell is blanked in the output</t>
+  </si>
+  <si>
+    <t>Linked product's SKU, blank on a free-text line or an unset SKU</t>
   </si>
   <si>
     <t>Line item description</t>
@@ -670,7 +679,8 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="2" min="1" width="28"/>
+    <col customWidth="true" max="1" min="1" width="16"/>
+    <col customWidth="true" max="2" min="2" width="40"/>
     <col customWidth="true" max="5" min="3" width="14"/>
   </cols>
   <sheetData>
@@ -748,44 +758,45 @@
       <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="C13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-  </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
@@ -805,76 +816,76 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -882,63 +893,63 @@
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -946,166 +957,174 @@
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="s">
-        <v>84</v>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" t="s">
-        <v>86</v>
+      <c r="A37" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="s">
-        <v>87</v>
+      <c r="B38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" t="s">
-        <v>89</v>
+      <c r="A39" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>93</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1113,8 +1132,8 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A39:C39"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/db/templates/inbound_delivery_default.xlsx
+++ b/db/templates/inbound_delivery_default.xlsx
@@ -679,7 +679,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="16"/>
+    <col customWidth="true" max="1" min="1" width="22"/>
     <col customWidth="true" max="2" min="2" width="40"/>
     <col customWidth="true" max="5" min="3" width="14"/>
   </cols>
